--- a/docs/StructureDefinition-BRProcedimentoRealizado-1.0.xlsx
+++ b/docs/StructureDefinition-BRProcedimentoRealizado-1.0.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>null (http://www.saude.gov.br)</t>
+    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br, cgiis.datasus@saude.gov.br)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -361,7 +361,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -927,7 +927,7 @@
     <t>Procedure.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -952,7 +952,7 @@
     <t>Procedure.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|ActivityDefinition|Measure|OperationDefinition|Questionnaire)
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1|Questionnaire|4.0.1)
 </t>
   </si>
   <si>
@@ -990,7 +990,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1013,7 +1013,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Procedure|Observation|MedicationAdministration)
+    <t xml:space="preserve">Reference(Procedure|4.0.1|Observation|4.0.1|MedicationAdministration|4.0.1)
 </t>
   </si>
   <si>
@@ -1081,7 +1081,7 @@
     <t>A code that identifies the reason a procedure was not performed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-not-performed-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-not-performed-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -1102,7 +1102,7 @@
     <t>A code that classifies a procedure for searching, sorting and display purposes.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-category</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-category|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
@@ -1367,7 +1367,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1412,7 +1412,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Procedure.subject.identifier.system</t>
@@ -1451,7 +1451,7 @@
     <t>Procedure.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1507,7 +1507,7 @@
     <t>Procedure.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson|Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1800,7 +1800,7 @@
     <t>Procedure.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -1834,7 +1834,7 @@
     <t>A code that identifies the reason a procedure is  required.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1849,7 +1849,7 @@
     <t>Procedure.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|Procedure|DiagnosticReport|DocumentReference)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|Procedure|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1)
 </t>
   </si>
   <si>
@@ -1881,7 +1881,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -1905,7 +1905,7 @@
     <t>An outcome of a procedure - whether it was resolved or otherwise.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-outcome</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-outcome|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=OUT].target.text</t>
@@ -1914,7 +1914,7 @@
     <t>Procedure.report</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DiagnosticReport|DocumentReference|Composition)
+    <t xml:space="preserve">Reference(DiagnosticReport|4.0.1|DocumentReference|4.0.1|Composition|4.0.1)
 </t>
   </si>
   <si>
@@ -1945,7 +1945,7 @@
     <t>Codes describing complications that resulted from a procedure.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=OUTC].target[classCode=OBS, code="complication", moodCode=EVN].value</t>
@@ -1954,7 +1954,7 @@
     <t>Procedure.complicationDetail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition)
+    <t xml:space="preserve">Reference(Condition|4.0.1)
 </t>
   </si>
   <si>
@@ -1979,7 +1979,7 @@
     <t>Specific follow up required for a procedure e.g. removal of sutures.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-followup</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-followup|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=ACT, moodCode=INT].code</t>
@@ -2016,7 +2016,7 @@
     <t>Procedure.note.author[x]</t>
   </si>
   <si>
-    <t>Reference(Practitioner|Patient|RelatedPerson|Organization)
+    <t>Reference(Practitioner|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 string</t>
   </si>
   <si>
@@ -2102,7 +2102,7 @@
     <t>A kind of change that happened to the device during the procedure.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/device-action</t>
+    <t>http://hl7.org/fhir/ValueSet/device-action|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="procedure device action"].value=:procedure device action codes</t>
@@ -2111,7 +2111,7 @@
     <t>Procedure.focalDevice.manipulated</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device)
+    <t xml:space="preserve">Reference(Device|4.0.1)
 </t>
   </si>
   <si>
@@ -2127,7 +2127,7 @@
     <t>Procedure.usedReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|Medication|Substance)
+    <t xml:space="preserve">Reference(Device|4.0.1|Medication|4.0.1|Substance|4.0.1)
 </t>
   </si>
   <si>
@@ -2159,7 +2159,7 @@
     <t>Codes describing items used during a procedure.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/device-kind</t>
+    <t>http://hl7.org/fhir/ValueSet/device-kind|4.0.1</t>
   </si>
   <si>
     <t>participation[typeCode=Dev].role[classCode=MANU]</t>
@@ -2645,7 +2645,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -4231,7 +4231,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>177</v>
       </c>
@@ -6971,7 +6971,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>326</v>
       </c>
@@ -7311,7 +7311,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>352</v>
       </c>
@@ -8683,7 +8683,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
         <v>373</v>
       </c>
@@ -9019,7 +9019,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>384</v>
       </c>
@@ -9357,7 +9357,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
         <v>394</v>
       </c>
@@ -9923,7 +9923,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
         <v>404</v>
       </c>
@@ -10489,7 +10489,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
         <v>411</v>
       </c>
@@ -12765,7 +12765,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
         <v>470</v>
       </c>
@@ -13103,7 +13103,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
         <v>490</v>
       </c>
@@ -13437,7 +13437,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="97" hidden="true">
+    <row r="97">
       <c r="A97" t="s" s="2">
         <v>498</v>
       </c>
@@ -13667,7 +13667,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="99" hidden="true">
+    <row r="99">
       <c r="A99" t="s" s="2">
         <v>508</v>
       </c>
@@ -15039,7 +15039,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="111" hidden="true">
+    <row r="111">
       <c r="A111" t="s" s="2">
         <v>528</v>
       </c>
@@ -16749,7 +16749,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="126" hidden="true">
+    <row r="126">
       <c r="A126" t="s" s="2">
         <v>553</v>
       </c>
@@ -19483,7 +19483,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="150" hidden="true">
+    <row r="150">
       <c r="A150" t="s" s="2">
         <v>634</v>
       </c>
@@ -20047,7 +20047,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="155" hidden="true">
+    <row r="155">
       <c r="A155" t="s" s="2">
         <v>655</v>
       </c>
@@ -21069,12 +21069,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN163">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
